--- a/regressoes/cdx_us_hy/excel/out/df_pval_exported.xlsx
+++ b/regressoes/cdx_us_hy/excel/out/df_pval_exported.xlsx
@@ -14,7 +14,19 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="48">
+  <si>
+    <t>Unnamed: 0</t>
+  </si>
+  <si>
+    <t>Codes</t>
+  </si>
+  <si>
+    <t>coef</t>
+  </si>
+  <si>
+    <t>pval</t>
+  </si>
   <si>
     <t>Names</t>
   </si>
@@ -67,6 +79,45 @@
     <t>16</t>
   </si>
   <si>
+    <t>fed_sloos_ci_small_firms_tight_q</t>
+  </si>
+  <si>
+    <t>global_pmi_comp</t>
+  </si>
+  <si>
+    <t>jpm_vol</t>
+  </si>
+  <si>
+    <t>move</t>
+  </si>
+  <si>
+    <t>ted_spread_us</t>
+  </si>
+  <si>
+    <t>vix</t>
+  </si>
+  <si>
+    <t>intercept</t>
+  </si>
+  <si>
+    <t>AIC</t>
+  </si>
+  <si>
+    <t>BIC</t>
+  </si>
+  <si>
+    <t>DW</t>
+  </si>
+  <si>
+    <t>LMpv</t>
+  </si>
+  <si>
+    <t>MSE</t>
+  </si>
+  <si>
+    <t>R2</t>
+  </si>
+  <si>
     <t>Fed Sloos Tight Std for C&amp;I Loans (Small Firms) (ZS) (Smoothed)</t>
   </si>
   <si>
@@ -83,27 +134,6 @@
   </si>
   <si>
     <t>VIX SPX</t>
-  </si>
-  <si>
-    <t>intercept</t>
-  </si>
-  <si>
-    <t>AIC</t>
-  </si>
-  <si>
-    <t>BIC</t>
-  </si>
-  <si>
-    <t>DW</t>
-  </si>
-  <si>
-    <t>LMpv</t>
-  </si>
-  <si>
-    <t>MSE</t>
-  </si>
-  <si>
-    <t>R2</t>
   </si>
   <si>
     <t>(0.0)</t>
@@ -485,10 +515,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q14"/>
+  <dimension ref="A1:U14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:17">
+    <row r="1" spans="1:21">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -540,426 +570,558 @@
       <c r="Q1" s="1" t="s">
         <v>16</v>
       </c>
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>20</v>
+      </c>
     </row>
-    <row r="2" spans="1:17">
-      <c r="A2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C2" t="s">
-        <v>30</v>
-      </c>
-      <c r="D2" t="s">
-        <v>30</v>
+    <row r="2" spans="1:21">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C2" t="b">
+        <v>0</v>
+      </c>
+      <c r="D2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E2" t="s">
+        <v>34</v>
+      </c>
+      <c r="G2" t="s">
+        <v>40</v>
+      </c>
+      <c r="H2" t="s">
+        <v>40</v>
       </c>
     </row>
-    <row r="3" spans="1:17">
-      <c r="A3" t="s">
-        <v>18</v>
+    <row r="3" spans="1:21">
+      <c r="A3">
+        <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>30</v>
-      </c>
-      <c r="D3" t="s">
-        <v>30</v>
+        <v>22</v>
+      </c>
+      <c r="C3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D3" t="b">
+        <v>1</v>
+      </c>
+      <c r="E3" t="s">
+        <v>35</v>
+      </c>
+      <c r="F3" t="s">
+        <v>40</v>
       </c>
       <c r="H3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I3" t="s">
-        <v>30</v>
-      </c>
-      <c r="J3" t="s">
-        <v>30</v>
-      </c>
-      <c r="K3" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="L3" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="M3" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="N3" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="O3" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="P3" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="Q3" t="s">
-        <v>30</v>
+        <v>40</v>
+      </c>
+      <c r="R3" t="s">
+        <v>40</v>
+      </c>
+      <c r="S3" t="s">
+        <v>40</v>
+      </c>
+      <c r="T3" t="s">
+        <v>40</v>
+      </c>
+      <c r="U3" t="s">
+        <v>40</v>
       </c>
     </row>
-    <row r="4" spans="1:17">
-      <c r="A4" t="s">
-        <v>19</v>
+    <row r="4" spans="1:21">
+      <c r="A4">
+        <v>5</v>
+      </c>
+      <c r="B4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4" t="b">
+        <v>0</v>
+      </c>
+      <c r="D4" t="b">
+        <v>1</v>
       </c>
       <c r="E4" t="s">
-        <v>30</v>
-      </c>
-      <c r="F4" t="s">
-        <v>30</v>
-      </c>
-      <c r="G4" t="s">
-        <v>30</v>
-      </c>
-      <c r="H4" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="I4" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="J4" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="K4" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="L4" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="M4" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="N4" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="O4" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="P4" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="Q4" t="s">
-        <v>30</v>
+        <v>40</v>
+      </c>
+      <c r="R4" t="s">
+        <v>40</v>
+      </c>
+      <c r="S4" t="s">
+        <v>40</v>
+      </c>
+      <c r="T4" t="s">
+        <v>40</v>
+      </c>
+      <c r="U4" t="s">
+        <v>40</v>
       </c>
     </row>
-    <row r="5" spans="1:17">
-      <c r="A5" t="s">
-        <v>20</v>
-      </c>
-      <c r="H5" t="s">
-        <v>32</v>
-      </c>
-      <c r="I5" t="s">
-        <v>33</v>
-      </c>
-      <c r="J5" t="s">
-        <v>30</v>
-      </c>
-      <c r="K5" t="s">
-        <v>35</v>
+    <row r="5" spans="1:21">
+      <c r="A5">
+        <v>7</v>
+      </c>
+      <c r="B5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5" t="b">
+        <v>0</v>
+      </c>
+      <c r="D5" t="b">
+        <v>1</v>
+      </c>
+      <c r="E5" t="s">
+        <v>37</v>
+      </c>
+      <c r="L5" t="s">
+        <v>42</v>
       </c>
       <c r="M5" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="N5" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="O5" t="s">
-        <v>32</v>
-      </c>
-      <c r="P5" t="s">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="Q5" t="s">
-        <v>32</v>
+        <v>42</v>
+      </c>
+      <c r="R5" t="s">
+        <v>42</v>
+      </c>
+      <c r="S5" t="s">
+        <v>42</v>
+      </c>
+      <c r="T5" t="s">
+        <v>42</v>
+      </c>
+      <c r="U5" t="s">
+        <v>42</v>
       </c>
     </row>
-    <row r="6" spans="1:17">
-      <c r="A6" t="s">
-        <v>21</v>
+    <row r="6" spans="1:21">
+      <c r="A6">
+        <v>9</v>
       </c>
       <c r="B6" t="s">
-        <v>30</v>
-      </c>
-      <c r="C6" t="s">
-        <v>30</v>
-      </c>
-      <c r="D6" t="s">
-        <v>30</v>
+        <v>25</v>
+      </c>
+      <c r="C6" t="b">
+        <v>0</v>
+      </c>
+      <c r="D6" t="b">
+        <v>1</v>
       </c>
       <c r="E6" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="F6" t="s">
-        <v>31</v>
+        <v>40</v>
+      </c>
+      <c r="G6" t="s">
+        <v>40</v>
+      </c>
+      <c r="H6" t="s">
+        <v>40</v>
       </c>
       <c r="I6" t="s">
-        <v>34</v>
-      </c>
-      <c r="K6" t="s">
-        <v>36</v>
-      </c>
-      <c r="L6" t="s">
-        <v>37</v>
+        <v>40</v>
+      </c>
+      <c r="J6" t="s">
+        <v>41</v>
+      </c>
+      <c r="M6" t="s">
+        <v>44</v>
+      </c>
+      <c r="O6" t="s">
+        <v>46</v>
+      </c>
+      <c r="P6" t="s">
+        <v>47</v>
       </c>
     </row>
-    <row r="7" spans="1:17">
-      <c r="A7" t="s">
-        <v>22</v>
-      </c>
-      <c r="F7" t="s">
-        <v>30</v>
-      </c>
-      <c r="G7" t="s">
-        <v>30</v>
-      </c>
-      <c r="H7" t="s">
-        <v>30</v>
+    <row r="7" spans="1:21">
+      <c r="A7">
+        <v>11</v>
+      </c>
+      <c r="B7" t="s">
+        <v>26</v>
+      </c>
+      <c r="C7" t="b">
+        <v>0</v>
+      </c>
+      <c r="D7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E7" t="s">
+        <v>39</v>
+      </c>
+      <c r="J7" t="s">
+        <v>40</v>
       </c>
       <c r="K7" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="L7" t="s">
-        <v>30</v>
-      </c>
-      <c r="M7" t="s">
-        <v>30</v>
-      </c>
-      <c r="N7" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="O7" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="P7" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="Q7" t="s">
-        <v>30</v>
+        <v>40</v>
+      </c>
+      <c r="R7" t="s">
+        <v>40</v>
+      </c>
+      <c r="S7" t="s">
+        <v>40</v>
+      </c>
+      <c r="T7" t="s">
+        <v>40</v>
+      </c>
+      <c r="U7" t="s">
+        <v>40</v>
       </c>
     </row>
-    <row r="8" spans="1:17">
-      <c r="A8" t="s">
-        <v>23</v>
+    <row r="8" spans="1:21">
+      <c r="A8">
+        <v>13</v>
       </c>
       <c r="B8" t="s">
-        <v>30</v>
-      </c>
-      <c r="C8" t="s">
-        <v>30</v>
-      </c>
-      <c r="D8" t="s">
-        <v>30</v>
+        <v>27</v>
+      </c>
+      <c r="C8" t="b">
+        <v>0</v>
+      </c>
+      <c r="D8" t="b">
+        <v>1</v>
       </c>
       <c r="E8" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="F8" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="G8" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="H8" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="I8" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="J8" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="K8" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="L8" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="M8" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="N8" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="O8" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="P8" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="Q8" t="s">
-        <v>30</v>
+        <v>40</v>
+      </c>
+      <c r="R8" t="s">
+        <v>40</v>
+      </c>
+      <c r="S8" t="s">
+        <v>40</v>
+      </c>
+      <c r="T8" t="s">
+        <v>40</v>
+      </c>
+      <c r="U8" t="s">
+        <v>40</v>
       </c>
     </row>
-    <row r="9" spans="1:17">
-      <c r="A9" t="s">
-        <v>24</v>
-      </c>
-      <c r="B9">
+    <row r="9" spans="1:21">
+      <c r="A9">
+        <v>14</v>
+      </c>
+      <c r="B9" t="s">
+        <v>28</v>
+      </c>
+      <c r="C9" t="b">
+        <v>0</v>
+      </c>
+      <c r="D9" t="b">
+        <v>0</v>
+      </c>
+      <c r="E9" t="s">
+        <v>28</v>
+      </c>
+      <c r="F9">
         <v>-1499.66</v>
       </c>
-      <c r="C9">
+      <c r="G9">
         <v>-1484.17</v>
       </c>
-      <c r="D9">
+      <c r="H9">
         <v>-1519.98</v>
       </c>
-      <c r="E9">
+      <c r="I9">
         <v>-1678.92</v>
       </c>
-      <c r="F9">
+      <c r="J9">
         <v>-1732.18</v>
       </c>
-      <c r="G9">
+      <c r="K9">
         <v>-1730.54</v>
       </c>
-      <c r="H9">
+      <c r="L9">
         <v>-1761.07</v>
       </c>
-      <c r="I9">
+      <c r="M9">
         <v>-1748.69</v>
       </c>
-      <c r="J9">
+      <c r="N9">
         <v>-1749.77</v>
       </c>
-      <c r="K9">
+      <c r="O9">
         <v>-1759.58</v>
       </c>
-      <c r="L9">
+      <c r="P9">
         <v>-1757.24</v>
-      </c>
-      <c r="M9">
-        <v>-1761.07</v>
-      </c>
-      <c r="N9">
-        <v>-1761.07</v>
-      </c>
-      <c r="O9">
-        <v>-1761.07</v>
-      </c>
-      <c r="P9">
-        <v>-1761.07</v>
       </c>
       <c r="Q9">
         <v>-1761.07</v>
       </c>
+      <c r="R9">
+        <v>-1761.07</v>
+      </c>
+      <c r="S9">
+        <v>-1761.07</v>
+      </c>
+      <c r="T9">
+        <v>-1761.07</v>
+      </c>
+      <c r="U9">
+        <v>-1761.07</v>
+      </c>
     </row>
-    <row r="10" spans="1:17">
-      <c r="A10" t="s">
-        <v>25</v>
-      </c>
-      <c r="B10">
+    <row r="10" spans="1:21">
+      <c r="A10">
+        <v>15</v>
+      </c>
+      <c r="B10" t="s">
+        <v>29</v>
+      </c>
+      <c r="C10" t="b">
+        <v>0</v>
+      </c>
+      <c r="D10" t="b">
+        <v>0</v>
+      </c>
+      <c r="E10" t="s">
+        <v>29</v>
+      </c>
+      <c r="F10">
         <v>-1488.94</v>
       </c>
-      <c r="C10">
+      <c r="G10">
         <v>-1473.45</v>
       </c>
-      <c r="D10">
+      <c r="H10">
         <v>-1505.67</v>
       </c>
-      <c r="E10">
+      <c r="I10">
         <v>-1668.19</v>
       </c>
-      <c r="F10">
+      <c r="J10">
         <v>-1717.88</v>
       </c>
-      <c r="G10">
+      <c r="K10">
         <v>-1719.81</v>
       </c>
-      <c r="H10">
+      <c r="L10">
         <v>-1743.19</v>
       </c>
-      <c r="I10">
+      <c r="M10">
         <v>-1730.81</v>
       </c>
-      <c r="J10">
+      <c r="N10">
         <v>-1735.47</v>
       </c>
-      <c r="K10">
+      <c r="O10">
         <v>-1738.13</v>
       </c>
-      <c r="L10">
+      <c r="P10">
         <v>-1739.36</v>
-      </c>
-      <c r="M10">
-        <v>-1743.19</v>
-      </c>
-      <c r="N10">
-        <v>-1743.19</v>
-      </c>
-      <c r="O10">
-        <v>-1743.19</v>
-      </c>
-      <c r="P10">
-        <v>-1743.19</v>
       </c>
       <c r="Q10">
         <v>-1743.19</v>
       </c>
+      <c r="R10">
+        <v>-1743.19</v>
+      </c>
+      <c r="S10">
+        <v>-1743.19</v>
+      </c>
+      <c r="T10">
+        <v>-1743.19</v>
+      </c>
+      <c r="U10">
+        <v>-1743.19</v>
+      </c>
     </row>
-    <row r="11" spans="1:17">
-      <c r="A11" t="s">
-        <v>26</v>
-      </c>
-      <c r="B11">
+    <row r="11" spans="1:21">
+      <c r="A11">
+        <v>16</v>
+      </c>
+      <c r="B11" t="s">
+        <v>30</v>
+      </c>
+      <c r="C11" t="b">
+        <v>0</v>
+      </c>
+      <c r="D11" t="b">
+        <v>0</v>
+      </c>
+      <c r="E11" t="s">
+        <v>30</v>
+      </c>
+      <c r="F11">
         <v>0.2</v>
       </c>
-      <c r="C11">
+      <c r="G11">
         <v>0.19</v>
       </c>
-      <c r="D11">
+      <c r="H11">
         <v>0.2</v>
       </c>
-      <c r="E11">
+      <c r="I11">
         <v>0.37</v>
       </c>
-      <c r="F11">
+      <c r="J11">
         <v>0.46</v>
       </c>
-      <c r="G11">
+      <c r="K11">
         <v>0.44</v>
       </c>
-      <c r="H11">
+      <c r="L11">
         <v>0.43</v>
       </c>
-      <c r="I11">
+      <c r="M11">
         <v>0.42</v>
       </c>
-      <c r="J11">
+      <c r="N11">
         <v>0.41</v>
-      </c>
-      <c r="K11">
-        <v>0.43</v>
-      </c>
-      <c r="L11">
-        <v>0.44</v>
-      </c>
-      <c r="M11">
-        <v>0.43</v>
-      </c>
-      <c r="N11">
-        <v>0.43</v>
       </c>
       <c r="O11">
         <v>0.43</v>
       </c>
       <c r="P11">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="Q11">
         <v>0.43</v>
       </c>
+      <c r="R11">
+        <v>0.43</v>
+      </c>
+      <c r="S11">
+        <v>0.43</v>
+      </c>
+      <c r="T11">
+        <v>0.43</v>
+      </c>
+      <c r="U11">
+        <v>0.43</v>
+      </c>
     </row>
-    <row r="12" spans="1:17">
-      <c r="A12" t="s">
-        <v>27</v>
-      </c>
-      <c r="B12">
-        <v>0</v>
-      </c>
-      <c r="C12">
-        <v>0</v>
-      </c>
-      <c r="D12">
-        <v>0</v>
-      </c>
-      <c r="E12">
-        <v>0</v>
+    <row r="12" spans="1:21">
+      <c r="A12">
+        <v>17</v>
+      </c>
+      <c r="B12" t="s">
+        <v>31</v>
+      </c>
+      <c r="C12" t="b">
+        <v>0</v>
+      </c>
+      <c r="D12" t="b">
+        <v>0</v>
+      </c>
+      <c r="E12" t="s">
+        <v>31</v>
       </c>
       <c r="F12">
         <v>0</v>
@@ -997,22 +1159,34 @@
       <c r="Q12">
         <v>0</v>
       </c>
+      <c r="R12">
+        <v>0</v>
+      </c>
+      <c r="S12">
+        <v>0</v>
+      </c>
+      <c r="T12">
+        <v>0</v>
+      </c>
+      <c r="U12">
+        <v>0</v>
+      </c>
     </row>
-    <row r="13" spans="1:17">
-      <c r="A13" t="s">
-        <v>28</v>
-      </c>
-      <c r="B13">
-        <v>0</v>
-      </c>
-      <c r="C13">
-        <v>0</v>
-      </c>
-      <c r="D13">
-        <v>0</v>
-      </c>
-      <c r="E13">
-        <v>0</v>
+    <row r="13" spans="1:21">
+      <c r="A13">
+        <v>18</v>
+      </c>
+      <c r="B13" t="s">
+        <v>32</v>
+      </c>
+      <c r="C13" t="b">
+        <v>0</v>
+      </c>
+      <c r="D13" t="b">
+        <v>0</v>
+      </c>
+      <c r="E13" t="s">
+        <v>32</v>
       </c>
       <c r="F13">
         <v>0</v>
@@ -1050,49 +1224,61 @@
       <c r="Q13">
         <v>0</v>
       </c>
+      <c r="R13">
+        <v>0</v>
+      </c>
+      <c r="S13">
+        <v>0</v>
+      </c>
+      <c r="T13">
+        <v>0</v>
+      </c>
+      <c r="U13">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:17">
-      <c r="A14" t="s">
-        <v>29</v>
-      </c>
-      <c r="B14">
+    <row r="14" spans="1:21">
+      <c r="A14">
+        <v>19</v>
+      </c>
+      <c r="B14" t="s">
+        <v>33</v>
+      </c>
+      <c r="C14" t="b">
+        <v>0</v>
+      </c>
+      <c r="D14" t="b">
+        <v>0</v>
+      </c>
+      <c r="E14" t="s">
+        <v>33</v>
+      </c>
+      <c r="F14">
         <v>0.45</v>
       </c>
-      <c r="C14">
+      <c r="G14">
         <v>0.42</v>
       </c>
-      <c r="D14">
+      <c r="H14">
         <v>0.5</v>
       </c>
-      <c r="E14">
+      <c r="I14">
         <v>0.72</v>
       </c>
-      <c r="F14">
+      <c r="J14">
         <v>0.77</v>
       </c>
-      <c r="G14">
+      <c r="K14">
         <v>0.77</v>
-      </c>
-      <c r="H14">
-        <v>0.8</v>
-      </c>
-      <c r="I14">
-        <v>0.79</v>
-      </c>
-      <c r="J14">
-        <v>0.79</v>
-      </c>
-      <c r="K14">
-        <v>0.8</v>
       </c>
       <c r="L14">
         <v>0.8</v>
       </c>
       <c r="M14">
-        <v>0.8</v>
+        <v>0.79</v>
       </c>
       <c r="N14">
-        <v>0.8</v>
+        <v>0.79</v>
       </c>
       <c r="O14">
         <v>0.8</v>
@@ -1101,6 +1287,18 @@
         <v>0.8</v>
       </c>
       <c r="Q14">
+        <v>0.8</v>
+      </c>
+      <c r="R14">
+        <v>0.8</v>
+      </c>
+      <c r="S14">
+        <v>0.8</v>
+      </c>
+      <c r="T14">
+        <v>0.8</v>
+      </c>
+      <c r="U14">
         <v>0.8</v>
       </c>
     </row>
